--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568751807</v>
+        <v>46157.93100869021</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93100869021</v>
+        <v>46157.93173818456</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93173818456</v>
+        <v>46157.93400554535</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400554535</v>
+        <v>46157.93718475327</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718475327</v>
+        <v>46158.28216774153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216774153</v>
+        <v>46158.29682189989</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29682189989</v>
+        <v>46158.29815198521</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815198521</v>
+        <v>46158.33387787678</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387787678</v>
+        <v>46158.36857604003</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/11. ООО ЛИКАРД (топливо Лукойл)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857604003</v>
+        <v>46158.37288216331</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
